--- a/Test/models/NEM_59bus_IASR.xlsx
+++ b/Test/models/NEM_59bus_IASR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\github\Test\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EF48E3-26DA-4740-AA98-4BB9922521DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64650DDD-85DA-4C01-98F5-CC5AD32EFE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,8 +99,29 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={31B3CE41-D465-49EF-BC57-B2B79999AA7B}</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{31B3CE41-D465-49EF-BC57-B2B79999AA7B}">
+      <text>
+        <t>[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    2 hours Utility Storage:
+Net. Cost 8000 $/MW - annual
+With T=8760h the marginal cost is 
+0.913 $/MW/h</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="273">
   <si>
     <t>N_101</t>
   </si>
@@ -913,13 +934,21 @@
   </si>
   <si>
     <t>SA_RefYear_2023_STEP_CHANGE_POE10_OPSO_MODELLING_PVLITE</t>
+  </si>
+  <si>
+    <t>Marginal Cost Charge ($/MWh)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marginal Cost Discharge ($/MWh)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,6 +962,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -989,6 +1025,7 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Luigi Teola" id="{2B007770-1A85-4A8D-A02E-BBB802DB410F}" userId="S::luigi.teola@sydney.edu.au::28556d9a-ea73-489f-aa18-fa7064f56df4" providerId="AD"/>
+  <person displayName="Zihao Qiu" id="{BDE48D56-D325-4A31-B2B8-3CD37F1F7BCC}" userId="S::zqiu0240@uni.sydney.edu.au::58a1009c-9152-45d1-8c34-6b4f708918ae" providerId="AD"/>
 </personList>
 </file>
 
@@ -1289,6 +1326,17 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="I1" dT="2026-03-29T13:07:25.09" personId="{BDE48D56-D325-4A31-B2B8-3CD37F1F7BCC}" id="{31B3CE41-D465-49EF-BC57-B2B79999AA7B}">
+    <text>2 hours Utility Storage:
+Net. Cost 8000 $/MW - annual
+With T=8760h the marginal cost is 
+0.913 $/MW/h</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3203C6-909C-49C6-92B8-75716A4181DA}">
   <dimension ref="A1:I111"/>
@@ -5684,21 +5732,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4ED449-B24C-41B9-B6BA-ED4D174B819D}">
-  <dimension ref="A1:H22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4ED449-B24C-41B9-B6BA-ED4D174B819D}">
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="2"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>95</v>
       </c>
@@ -5723,8 +5773,14 @@
       <c r="H1" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>248</v>
       </c>
@@ -5751,8 +5807,15 @@
       <c r="H2" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <f>0.913*E2</f>
+        <v>95.865000000000009</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>246</v>
       </c>
@@ -5779,8 +5842,15 @@
       <c r="H3" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <f t="shared" ref="I3:I22" si="2">0.913*E3</f>
+        <v>209.99</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>247</v>
       </c>
@@ -5807,8 +5877,15 @@
       <c r="H4" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>228.25</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>249</v>
       </c>
@@ -5835,8 +5912,15 @@
       <c r="H5" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>35.606999999999999</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>251</v>
       </c>
@@ -5863,8 +5947,15 @@
       <c r="H6" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>50.215000000000003</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>250</v>
       </c>
@@ -5891,8 +5982,15 @@
       <c r="H7" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>73.040000000000006</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>252</v>
       </c>
@@ -5919,8 +6017,15 @@
       <c r="H8" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>136.95000000000002</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -5947,8 +6052,15 @@
       <c r="H9" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>254</v>
       </c>
@@ -5975,8 +6087,15 @@
       <c r="H10" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>13.695</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>255</v>
       </c>
@@ -6003,8 +6122,15 @@
       <c r="H11" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>2.2825000000000002</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>256</v>
       </c>
@@ -6031,8 +6157,15 @@
       <c r="H12" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>365.2</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>257</v>
       </c>
@@ -6059,8 +6192,15 @@
       <c r="H13" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>136.95000000000002</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>258</v>
       </c>
@@ -6087,8 +6227,15 @@
       <c r="H14" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>22.824999999999999</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>259</v>
       </c>
@@ -6115,8 +6262,15 @@
       <c r="H15" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>91.3</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>260</v>
       </c>
@@ -6143,8 +6297,15 @@
       <c r="H16" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>91.3</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>261</v>
       </c>
@@ -6171,8 +6332,15 @@
       <c r="H17" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>136.95000000000002</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>262</v>
       </c>
@@ -6199,8 +6367,15 @@
       <c r="H18" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>237.8365</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>263</v>
       </c>
@@ -6227,8 +6402,15 @@
       <c r="H19" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>114.58150000000001</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>264</v>
       </c>
@@ -6255,8 +6437,15 @@
       <c r="H20" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>13.695</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>265</v>
       </c>
@@ -6283,8 +6472,15 @@
       <c r="H21" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>26.020500000000002</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>266</v>
       </c>
@@ -6311,9 +6507,18 @@
       <c r="H22" s="2">
         <v>90</v>
       </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>11.4125</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>